--- a/data/Chemical_analysis_raw/260212_EEWORM_these Lisa_worms_MIX.xlsx
+++ b/data/Chemical_analysis_raw/260212_EEWORM_these Lisa_worms_MIX.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisagollot/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisagollot/Library/CloudStorage/OneDrive-Personnel/Documents/0_These/0_RepoGit/Ew-Mix-TK/data/Chemical_analysis_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2DF88F-A330-F14B-B41E-37F353FB10B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8F2C42-C22B-B040-BFE4-11B14A1150AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29220" windowHeight="18240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29220" windowHeight="18240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="facteur récupération" sheetId="2" r:id="rId1"/>
